--- a/ig/document/StructureDefinition-medcom-document-bundle.xlsx
+++ b/ig/document/StructureDefinition-medcom-document-bundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>2.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-14T10:37:57+00:00</t>
+    <t>2026-03-10T10:54:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1459,7 +1459,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>85</v>
       </c>
@@ -1913,7 +1913,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>115</v>
       </c>
@@ -2027,7 +2027,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>122</v>
       </c>
@@ -2141,7 +2141,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="9" hidden="true">
+    <row r="9">
       <c r="A9" t="s" s="2">
         <v>131</v>
       </c>
@@ -3049,7 +3049,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
         <v>176</v>
       </c>
@@ -3615,7 +3615,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
         <v>186</v>
       </c>
@@ -3729,7 +3729,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>190</v>
       </c>
@@ -6789,12 +6789,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN49">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/ig/document/StructureDefinition-medcom-document-bundle.xlsx
+++ b/ig/document/StructureDefinition-medcom-document-bundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.1</t>
+    <t>2.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T10:54:08+00:00</t>
+    <t>2026-04-29T08:07:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
